--- a/data/club_list.xlsx
+++ b/data/club_list.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,67 +443,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>광대</t>
+          <t>꿈빛 파티시엘</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>밴드</t>
+          <t>베이킹</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>글로우</t>
+          <t>무브먼트</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>밴드</t>
+          <t>댄스</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라이트</t>
+          <t>밥먹을래? 빵먹을래?[밥:빵]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>밴드</t>
+          <t>베이킹</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>라인</t>
+          <t>빵글빵글</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>밴드</t>
+          <t>베이킹</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루미너스</t>
+          <t>빵야빵야</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>밴드</t>
+          <t>베이킹</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>미:연</t>
+          <t>슈퍼스타</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>밴디름</t>
+          <t>시계꽃</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>보히</t>
+          <t>헤르츠</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,19 +539,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>블리스</t>
+          <t>헤어밴드</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>댄스</t>
+          <t>밴드</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>샛별</t>
+          <t>Amitie</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>시온</t>
+          <t>Forever</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -575,19 +575,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>아크로체</t>
+          <t>Growve</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>미술</t>
+          <t>댄스</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>유니스</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -599,43 +599,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>초청</t>
+          <t>Noella</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>밴드</t>
+          <t>댄스</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>클러스터</t>
+          <t>SMILE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>댄스</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>클로버</t>
+          <t>Sprout</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>댄스</t>
+          <t>밴드</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>투핸드</t>
+          <t>The Way</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -647,130 +647,10 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>퍼스트</t>
+          <t>We fly</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
-        <is>
-          <t>밴드</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>포커스</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>밴드</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>하모리</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>미술</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>하이라이트</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>밴드</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>하이애니드림하이</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>여가</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>혼동</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>댄스</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>히어로</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>연극</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AFFECT</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>댄스</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>S.P</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>밴드</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>WeCD</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>밴드</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Will win</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
         <is>
           <t>댄스</t>
         </is>
